--- a/investor_forms/014_investment_bonds_survey--investor_forms.xlsx
+++ b/investor_forms/014_investment_bonds_survey--investor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,179 +520,271 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>investment_bonds_survey_page_1</t>
+          <t>investment_goals</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>What are your investment goals for the next 6-12 months?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>risk_tolerance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>What is your risk tolerance level?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>investment_amount</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>How much money do you plan to invest in bonds?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>investment_experience</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>What is your investment experience level?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>bond_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>Which type of bond are you most interested in?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>income_level</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>What is your current income level?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>investment_frequency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>How often do you expect to invest in bonds?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>time_horizon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in</t>
+          <t>What is your time horizon for investment in bonds?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bond_size</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>How much do you expect to invest in a single bond?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>yield_preference</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Are you interested in investing in bonds with a high-yield or low-yield option?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>term_preference</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>What is your preferred bond term?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>information_source</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>What is your primary source of information for investment decisions?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -707,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,272 +827,595 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>investment_bonds_survey_page_1_choices</t>
+          <t>investment_goals_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>short-term_(less_than_1_year)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Short-term (less than 1 year)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>investment_bonds_survey_page_1_choices</t>
+          <t>investment_goals_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>medium-term_(1-5_years)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Medium-term (1-5 years)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>investment_goals_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>long-term_(more_than_5_years)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Long-term (more than 5 years)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>risk_tolerance_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>risk_tolerance_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>risk_tolerance_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>investment_amount_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>less_than_$1000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Less than $1000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>investment_amount_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>$1000-$5000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$1000-$5000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>investment_amount_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>more_than_$5000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>More than $5000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>investment_experience_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>investment_experience_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>investment_experience_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>bond_type_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>government_bonds</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Government bonds</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>bond_type_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>corporate_bonds</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Corporate bonds</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>bond_type_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>municipal_bonds</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Municipal bonds</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>what_bonds_are_you_interested_in_choices</t>
+          <t>income_level_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>less_than_$50,000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Less than $50,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>income_level_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>$50,000-$75,000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>$50,000-$75,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>income_level_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>more_than_$75,000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>More than $75,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>investment_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>investment_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investment_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>annually</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Annually</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>time_horizon_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>less_than_1_year</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Less than 1 year</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>time_horizon_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1-5_years</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>time_horizon_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>more_than_5_years</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>More than 5 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>bond_size_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>less_than_$10,000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Less than $10,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>bond_size_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>$10,000-$50,000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>$10,000-$50,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>bond_size_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>more_than_$50,000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>More than $50,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>yield_preference_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>yield_preference_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>term_preference_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>short-term_(less_than_1_year)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Short-term (less than 1 year)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>term_preference_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>medium-term_(1-5_years)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Medium-term (1-5 years)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>term_preference_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>long-term_(more_than_5_years)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Long-term (more than 5 years)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>information_source_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>financial_advisor</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Financial advisor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>information_source_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>online_research</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Online research</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>information_source_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>word_of_mouth</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Word of mouth</t>
         </is>
       </c>
     </row>
